--- a/realstep-head/catalog/products.xlsx
+++ b/realstep-head/catalog/products.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c262efc70aa72104/Documents/catalogo_head/Catalogo_Head/realstep-head/catalog/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1856" documentId="11_ADE01E1E62D19FE47686E5DB2F4B9CE89BB4BB42" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{275D5430-E245-450D-8E4E-00CF3FB95A93}"/>
+  <xr:revisionPtr revIDLastSave="1859" documentId="11_ADE01E1E62D19FE47686E5DB2F4B9CE89BB4BB42" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08025060-A83F-4BC4-9CB1-19BF296D40D9}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Categorias" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6553" uniqueCount="1201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6561" uniqueCount="1201">
   <si>
     <t>producto_id</t>
   </si>
@@ -13457,7 +13457,7 @@
         <v>1175</v>
       </c>
       <c r="C115" s="14" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="D115" s="14"/>
       <c r="E115" s="14"/>

--- a/realstep-head/catalog/products.xlsx
+++ b/realstep-head/catalog/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\catalogo_head\Catalogo_Head\realstep-head\catalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFF2C99F-697D-44D1-96B5-58E0B2A929E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631D3EB6-017B-461D-947C-D50B616F8B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12233,7 +12233,7 @@
         <v>183300</v>
       </c>
       <c r="H64" s="31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" s="31" t="s">
         <v>198</v>
@@ -13100,7 +13100,7 @@
         <v>186612</v>
       </c>
       <c r="H95" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I95" s="4" t="s">
         <v>198</v>
@@ -13464,7 +13464,7 @@
         <v>171060</v>
       </c>
       <c r="H108" s="14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I108" s="14" t="s">
         <v>198</v>
@@ -14215,7 +14215,7 @@
         <v>259188</v>
       </c>
       <c r="H135" s="14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I135" s="14" t="s">
         <v>198</v>
